--- a/artfynd/A 12455-2024 artfynd.xlsx
+++ b/artfynd/A 12455-2024 artfynd.xlsx
@@ -7227,7 +7227,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117658665</v>
+        <v>117658669</v>
       </c>
       <c r="B65" t="n">
         <v>57287</v>
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>417051</v>
+        <v>417309</v>
       </c>
       <c r="R65" t="n">
-        <v>7045298</v>
+        <v>7045360</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre och något nyare</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7334,7 +7334,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117658669</v>
+        <v>117658665</v>
       </c>
       <c r="B66" t="n">
         <v>57287</v>
@@ -7374,10 +7374,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>417309</v>
+        <v>417051</v>
       </c>
       <c r="R66" t="n">
-        <v>7045360</v>
+        <v>7045298</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack äldre och något nyare</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 12455-2024 artfynd.xlsx
+++ b/artfynd/A 12455-2024 artfynd.xlsx
@@ -6916,7 +6916,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117658673</v>
+        <v>117658674</v>
       </c>
       <c r="B62" t="n">
         <v>97857</v>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>417040</v>
+        <v>417203</v>
       </c>
       <c r="R62" t="n">
-        <v>7045359</v>
+        <v>7045331</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7018,7 +7018,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117658670</v>
+        <v>117658665</v>
       </c>
       <c r="B63" t="n">
         <v>57287</v>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>417367</v>
+        <v>417051</v>
       </c>
       <c r="R63" t="n">
-        <v>7045344</v>
+        <v>7045298</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7125,10 +7125,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117658677</v>
+        <v>117658668</v>
       </c>
       <c r="B64" t="n">
-        <v>90941</v>
+        <v>57287</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7137,25 +7137,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7165,10 +7165,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>417236</v>
+        <v>417304</v>
       </c>
       <c r="R64" t="n">
-        <v>7045238</v>
+        <v>7045461</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7201,6 +7201,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7227,10 +7232,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117658669</v>
+        <v>117658673</v>
       </c>
       <c r="B65" t="n">
-        <v>57287</v>
+        <v>97857</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7239,25 +7244,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7267,10 +7272,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>417309</v>
+        <v>417040</v>
       </c>
       <c r="R65" t="n">
-        <v>7045360</v>
+        <v>7045359</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7303,11 +7308,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack äldre och något nyare</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7334,7 +7334,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117658665</v>
+        <v>117658670</v>
       </c>
       <c r="B66" t="n">
         <v>57287</v>
@@ -7374,10 +7374,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>417051</v>
+        <v>417367</v>
       </c>
       <c r="R66" t="n">
-        <v>7045298</v>
+        <v>7045344</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7441,7 +7441,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117658668</v>
+        <v>117658669</v>
       </c>
       <c r="B67" t="n">
         <v>57287</v>
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>417304</v>
+        <v>417309</v>
       </c>
       <c r="R67" t="n">
-        <v>7045461</v>
+        <v>7045360</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre och något nyare</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7548,10 +7548,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117658622</v>
+        <v>117658677</v>
       </c>
       <c r="B68" t="n">
-        <v>90499</v>
+        <v>90941</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7560,25 +7560,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>417286</v>
+        <v>417236</v>
       </c>
       <c r="R68" t="n">
-        <v>7045449</v>
+        <v>7045238</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7650,10 +7650,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117658685</v>
+        <v>117658676</v>
       </c>
       <c r="B69" t="n">
-        <v>90517</v>
+        <v>57303</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7666,21 +7666,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>417220</v>
+        <v>416980</v>
       </c>
       <c r="R69" t="n">
-        <v>7045627</v>
+        <v>7045361</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7726,6 +7726,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7752,10 +7757,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117658693</v>
+        <v>117658685</v>
       </c>
       <c r="B70" t="n">
-        <v>78480</v>
+        <v>90517</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7768,21 +7773,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7792,10 +7797,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>417170</v>
+        <v>417220</v>
       </c>
       <c r="R70" t="n">
-        <v>7045271</v>
+        <v>7045627</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7828,11 +7833,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7859,10 +7859,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117658667</v>
+        <v>117658622</v>
       </c>
       <c r="B71" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7875,21 +7875,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7899,10 +7899,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>417312</v>
+        <v>417286</v>
       </c>
       <c r="R71" t="n">
-        <v>7045373</v>
+        <v>7045449</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7935,11 +7935,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7966,10 +7961,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117658676</v>
+        <v>117658693</v>
       </c>
       <c r="B72" t="n">
-        <v>57303</v>
+        <v>78480</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7982,21 +7977,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8006,10 +8001,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>416980</v>
+        <v>417170</v>
       </c>
       <c r="R72" t="n">
-        <v>7045361</v>
+        <v>7045271</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8046,7 +8041,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8180,10 +8175,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117658674</v>
+        <v>117658667</v>
       </c>
       <c r="B74" t="n">
-        <v>97857</v>
+        <v>57287</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8192,25 +8187,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8220,10 +8215,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>417203</v>
+        <v>417312</v>
       </c>
       <c r="R74" t="n">
-        <v>7045331</v>
+        <v>7045373</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8256,6 +8251,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 12455-2024 artfynd.xlsx
+++ b/artfynd/A 12455-2024 artfynd.xlsx
@@ -6817,7 +6817,7 @@
         <v>117278987</v>
       </c>
       <c r="B61" t="n">
-        <v>74592</v>
+        <v>74594</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6916,10 +6916,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117658674</v>
+        <v>117658667</v>
       </c>
       <c r="B62" t="n">
-        <v>97857</v>
+        <v>57288</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6928,25 +6928,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>417203</v>
+        <v>417312</v>
       </c>
       <c r="R62" t="n">
-        <v>7045331</v>
+        <v>7045373</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6992,6 +6992,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7018,10 +7023,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117658665</v>
+        <v>117658676</v>
       </c>
       <c r="B63" t="n">
-        <v>57287</v>
+        <v>57304</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7034,16 +7039,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7058,10 +7063,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>417051</v>
+        <v>416980</v>
       </c>
       <c r="R63" t="n">
-        <v>7045298</v>
+        <v>7045361</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7098,7 +7103,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7128,7 +7133,7 @@
         <v>117658668</v>
       </c>
       <c r="B64" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7232,10 +7237,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117658673</v>
+        <v>117658670</v>
       </c>
       <c r="B65" t="n">
-        <v>97857</v>
+        <v>57288</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7244,25 +7249,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7272,10 +7277,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>417040</v>
+        <v>417367</v>
       </c>
       <c r="R65" t="n">
-        <v>7045359</v>
+        <v>7045344</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7308,6 +7313,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7334,10 +7344,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117658670</v>
+        <v>117658674</v>
       </c>
       <c r="B66" t="n">
-        <v>57287</v>
+        <v>97859</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7346,25 +7356,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7374,10 +7384,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>417367</v>
+        <v>417203</v>
       </c>
       <c r="R66" t="n">
-        <v>7045344</v>
+        <v>7045331</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7410,11 +7420,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7441,10 +7446,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117658669</v>
+        <v>117658695</v>
       </c>
       <c r="B67" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7457,21 +7462,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7481,10 +7486,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>417309</v>
+        <v>417175</v>
       </c>
       <c r="R67" t="n">
-        <v>7045360</v>
+        <v>7045345</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7517,11 +7522,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack äldre och något nyare</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7548,10 +7548,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117658677</v>
+        <v>117658665</v>
       </c>
       <c r="B68" t="n">
-        <v>90941</v>
+        <v>57288</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7560,25 +7560,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>417236</v>
+        <v>417051</v>
       </c>
       <c r="R68" t="n">
-        <v>7045238</v>
+        <v>7045298</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7624,6 +7624,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7650,10 +7655,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117658676</v>
+        <v>117658685</v>
       </c>
       <c r="B69" t="n">
-        <v>57303</v>
+        <v>90519</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7666,21 +7671,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7690,10 +7695,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>416980</v>
+        <v>417220</v>
       </c>
       <c r="R69" t="n">
-        <v>7045361</v>
+        <v>7045627</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7726,11 +7731,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7757,10 +7757,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117658685</v>
+        <v>117658666</v>
       </c>
       <c r="B70" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7773,21 +7773,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>417220</v>
+        <v>417126</v>
       </c>
       <c r="R70" t="n">
-        <v>7045627</v>
+        <v>7045217</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7833,6 +7833,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7859,10 +7864,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117658622</v>
+        <v>117658669</v>
       </c>
       <c r="B71" t="n">
-        <v>90499</v>
+        <v>57288</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7875,21 +7880,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7899,10 +7904,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>417286</v>
+        <v>417309</v>
       </c>
       <c r="R71" t="n">
-        <v>7045449</v>
+        <v>7045360</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7935,6 +7940,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack äldre och något nyare</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7961,10 +7971,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117658693</v>
+        <v>117658622</v>
       </c>
       <c r="B72" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7977,21 +7987,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8001,10 +8011,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>417170</v>
+        <v>417286</v>
       </c>
       <c r="R72" t="n">
-        <v>7045271</v>
+        <v>7045449</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8037,11 +8047,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8068,10 +8073,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117658666</v>
+        <v>117658673</v>
       </c>
       <c r="B73" t="n">
-        <v>57287</v>
+        <v>97859</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8080,25 +8085,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8108,10 +8113,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>417126</v>
+        <v>417040</v>
       </c>
       <c r="R73" t="n">
-        <v>7045217</v>
+        <v>7045359</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8144,11 +8149,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8175,10 +8175,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117658667</v>
+        <v>117658677</v>
       </c>
       <c r="B74" t="n">
-        <v>57287</v>
+        <v>90943</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8187,25 +8187,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8215,10 +8215,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>417312</v>
+        <v>417236</v>
       </c>
       <c r="R74" t="n">
-        <v>7045373</v>
+        <v>7045238</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8251,11 +8251,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8282,10 +8277,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117658695</v>
+        <v>117658693</v>
       </c>
       <c r="B75" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8322,10 +8317,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>417175</v>
+        <v>417170</v>
       </c>
       <c r="R75" t="n">
-        <v>7045345</v>
+        <v>7045271</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8358,6 +8353,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD75" t="b">
